--- a/配置表格/C词条表.xlsx
+++ b/配置表格/C词条表.xlsx
@@ -473,13 +473,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DN50"/>
+  <dimension ref="A1:DN87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22.1" customWidth="1" min="4" max="4"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="110" customWidth="1"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
@@ -592,7 +592,7 @@
     <col width="16.9" customWidth="1" min="115" max="115"/>
     <col width="15.6" customWidth="1" min="116" max="116"/>
     <col width="15.6" customWidth="1" min="117" max="117"/>
-    <col width="30" customWidth="1" min="118" max="118"/>
+    <col min="118" max="118" width="110" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4148,6 +4148,2045 @@
         </is>
       </c>
     </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" t="n">
+        <v>60001</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·剑道凝威</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】剑道神通基础威力提高5%。</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">剑道</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基础威力</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>500</v>
+      </c>
+      <c r="DN51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" t="n">
+        <v>60002</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·剑道回转</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】剑道神通冷却总时长降低5%，不改变已开始的剩余计时。</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">剑道</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冷却时间</t>
+        </is>
+      </c>
+      <c r="S52" t="n">
+        <v>-500</v>
+      </c>
+      <c r="DN52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" t="n">
+        <v>60003</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·炼体凝威</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】炼体神通基础威力提高5%。</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">炼体</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基础威力</t>
+        </is>
+      </c>
+      <c r="S53" t="n">
+        <v>500</v>
+      </c>
+      <c r="DN53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" t="n">
+        <v>60004</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·炼体回转</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】炼体神通冷却总时长降低5%，不改变已开始的剩余计时。</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">炼体</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冷却时间</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
+        <v>-500</v>
+      </c>
+      <c r="DN54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" t="n">
+        <v>60005</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·五行凝威</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】五行神通基础威力提高5%。</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">五行</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基础威力</t>
+        </is>
+      </c>
+      <c r="S55" t="n">
+        <v>500</v>
+      </c>
+      <c r="DN55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" t="n">
+        <v>60006</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·五行回转</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】五行神通冷却总时长降低5%，不改变已开始的剩余计时。</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">五行</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冷却时间</t>
+        </is>
+      </c>
+      <c r="S56" t="n">
+        <v>-500</v>
+      </c>
+      <c r="DN56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" t="n">
+        <v>60007</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·金行凝威</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】金行神通基础威力提高5%。</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金行</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基础威力</t>
+        </is>
+      </c>
+      <c r="S57" t="n">
+        <v>500</v>
+      </c>
+      <c r="DN57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" t="n">
+        <v>60008</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·金行回转</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】金行神通冷却总时长降低5%，不改变已开始的剩余计时。</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金行</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冷却时间</t>
+        </is>
+      </c>
+      <c r="S58" t="n">
+        <v>-500</v>
+      </c>
+      <c r="DN58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" t="n">
+        <v>60009</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·木行凝威</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】木行神通基础威力提高5%。</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">木行</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基础威力</t>
+        </is>
+      </c>
+      <c r="S59" t="n">
+        <v>500</v>
+      </c>
+      <c r="DN59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" t="n">
+        <v>60010</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·木行回转</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】木行神通冷却总时长降低5%，不改变已开始的剩余计时。</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">木行</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冷却时间</t>
+        </is>
+      </c>
+      <c r="S60" t="n">
+        <v>-500</v>
+      </c>
+      <c r="DN60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" t="n">
+        <v>60011</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·水行凝威</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】水行神通基础威力提高5%。</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水行</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基础威力</t>
+        </is>
+      </c>
+      <c r="S61" t="n">
+        <v>500</v>
+      </c>
+      <c r="DN61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="B62" t="n">
+        <v>60012</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·水行回转</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】水行神通冷却总时长降低5%，不改变已开始的剩余计时。</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水行</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冷却时间</t>
+        </is>
+      </c>
+      <c r="S62" t="n">
+        <v>-500</v>
+      </c>
+      <c r="DN62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="B63" t="n">
+        <v>60013</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·火行凝威</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】火行神通基础威力提高5%。</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火行</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基础威力</t>
+        </is>
+      </c>
+      <c r="S63" t="n">
+        <v>500</v>
+      </c>
+      <c r="DN63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="B64" t="n">
+        <v>60014</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·火行回转</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】火行神通冷却总时长降低5%，不改变已开始的剩余计时。</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火行</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冷却时间</t>
+        </is>
+      </c>
+      <c r="S64" t="n">
+        <v>-500</v>
+      </c>
+      <c r="DN64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="B65" t="n">
+        <v>60015</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·土行凝威</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】土行神通基础威力提高5%。</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">土行</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基础威力</t>
+        </is>
+      </c>
+      <c r="S65" t="n">
+        <v>500</v>
+      </c>
+      <c r="DN65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="B66" t="n">
+        <v>60016</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·土行回转</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】土行神通冷却总时长降低5%，不改变已开始的剩余计时。</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">土行</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冷却时间</t>
+        </is>
+      </c>
+      <c r="S66" t="n">
+        <v>-500</v>
+      </c>
+      <c r="DN66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="B67" t="n">
+        <v>60017</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·术法凝威</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】术法神通基础威力提高5%。</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">术法</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基础威力</t>
+        </is>
+      </c>
+      <c r="S67" t="n">
+        <v>500</v>
+      </c>
+      <c r="DN67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="B68" t="n">
+        <v>60018</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·术法回转</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】术法神通冷却总时长降低5%，不改变已开始的剩余计时。</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系别</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">术法</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冷却时间</t>
+        </is>
+      </c>
+      <c r="S68" t="n">
+        <v>-500</v>
+      </c>
+      <c r="DN68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】正式平衡前可改名、改值；此行为有效导出数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="B69" t="n">
+        <v>60101</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·养锋精进</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·养锋状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219001</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S69" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="B70" t="n">
+        <v>60102</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·引灵精进</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·引灵状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219002</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S70" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="B71" t="n">
+        <v>60103</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·破军精进</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·破军状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219003</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S71" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="B72" t="n">
+        <v>60104</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·疾行精进</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·疾行状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219004</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S72" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="B73" t="n">
+        <v>60105</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·轻灵精进</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·轻灵状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219005</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="B74" t="n">
+        <v>60106</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·避法精进</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·避法状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219006</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S74" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="B75" t="n">
+        <v>60107</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·厚甲精进</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·厚甲状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219007</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S75" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="B76" t="n">
+        <v>60108</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·御法精进</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·御法状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219008</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S76" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="B77" t="n">
+        <v>60109</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·凝神精进</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·凝神状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219009</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S77" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="B78" t="n">
+        <v>60110</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·护法精进</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·护法状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219010</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S78" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="B79" t="n">
+        <v>60111</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·镇压精进</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·镇压施加的眩晕持续时间提高20%。</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219011</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">持续时间</t>
+        </is>
+      </c>
+      <c r="S79" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="B80" t="n">
+        <v>60112</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·破势精进</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·破势状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219012</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S80" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="B81" t="n">
+        <v>60113</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·护身精进</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·护身状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219013</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S81" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="B82" t="n">
+        <v>60114</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·凝元精进</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·凝元状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219014</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S82" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="B83" t="n">
+        <v>60115</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·金曜精进</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·金曜状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219015</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S83" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="B84" t="n">
+        <v>60116</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·青荣精进</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·青荣状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219016</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S84" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="B85" t="n">
+        <v>60117</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·沧澜精进</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·沧澜状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219017</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S85" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="B86" t="n">
+        <v>60118</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·离火精进</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·离火状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219018</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S86" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="B87" t="n">
+        <v>60119</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试配·玄岳精进</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】器法·玄岳状态提供的属性修正数值提高20%。</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219019</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增减</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">属性修正数值</t>
+        </is>
+      </c>
+      <c r="S87" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DN87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【开发试配】需有对应器法状态才生效；词条不授予器法。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="E1:H1"/>
